--- a/reports/pdf_weekly_20260703.xlsx
+++ b/reports/pdf_weekly_20260703.xlsx
@@ -570,7 +570,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 6,036억      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -666,10 +666,10 @@
         <v>52</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>552687720</v>
+        <v>563306120</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         <v>-57</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-4924971000</v>
+        <v>-5019591000</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         <v>33</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1460002500</v>
+        <v>1488052500</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.242</v>
+        <v>0.279</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>-49</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2688174300</v>
+        <v>-2739820300</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-0.445</v>
+        <v>-0.513</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>531503370</v>
+        <v>541714770</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         <v>-46</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-4836486000</v>
+        <v>-4929406000</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.801</v>
+        <v>-0.923</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
         <v>27</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1086335550</v>
+        <v>1107206550</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.18</v>
+        <v>0.207</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         <v>-36</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-504426960</v>
+        <v>-514118160</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.096</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2054309400</v>
+        <v>2093777400</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.34</v>
+        <v>0.392</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-4592996100</v>
+        <v>-4681238100</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-0.761</v>
+        <v>-0.876</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2054934000</v>
+        <v>2094414000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.34</v>
+        <v>0.392</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>-24</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2171109600</v>
+        <v>-2212821600</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-0.36</v>
+        <v>-0.414</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>14</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1890247800</v>
+        <v>1926563800</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.313</v>
+        <v>0.361</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1700994000</v>
+        <v>-1733674000</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-0.282</v>
+        <v>-0.325</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>531326400</v>
+        <v>541534400</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-3029310000</v>
+        <v>-3087510000</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-0.502</v>
+        <v>-0.578</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1464687000</v>
+        <v>1492827000</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.243</v>
+        <v>0.28</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>-3</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-768258000</v>
+        <v>-783018000</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-0.127</v>
+        <v>-0.147</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2251683000</v>
+        <v>2294943000</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.373</v>
+        <v>0.43</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>429100200</v>
+        <v>437344200</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>451273500</v>
+        <v>459943500</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.075</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1463646000</v>
+        <v>1491766000</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.242</v>
+        <v>0.279</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         <v>3</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>708921000</v>
+        <v>722541000</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.117</v>
+        <v>0.135</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,954억      주말 2026-07-03  vs  주초 2026-06-29      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      주말 2026-07-03  vs  주초 2026-06-29      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1245,10 +1245,10 @@
         <v>68</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>447265920</v>
+        <v>454352880</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         <v>-20</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1781248000</v>
+        <v>-1809472000</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>-0.36</v>
+        <v>-0.372</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1485888000</v>
+        <v>1509432000</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.3</v>
+        <v>0.311</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,774억      주말 2026-07-03  vs  주초 2026-06-29      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,365억      주말 2026-07-03  vs  주초 2026-06-29      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1400,10 +1400,10 @@
         <v>21</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>2512406400</v>
+        <v>2532163200</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.666</v>
+        <v>0.752</v>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         <v>-39</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-2669202900</v>
+        <v>-2690192700</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>-0.707</v>
+        <v>-0.799</v>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,898억      주말 2026-07-03  vs  주초 2026-06-29      매수 0종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,838억      주말 2026-07-03  vs  주초 2026-06-29      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1534,10 +1534,10 @@
         <v>-5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-345253000</v>
+        <v>-351434000</v>
       </c>
       <c r="J35" s="16" t="n">
-        <v>-0.119</v>
+        <v>-0.124</v>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 394억      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 13종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1644,10 +1644,10 @@
         <v>80</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>68572000</v>
+        <v>63808000</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
         <v>-111</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-245970450</v>
+        <v>-216672000</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>-0.624</v>
+        <v>-0.61</v>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
         <v>29</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>111113500</v>
+        <v>106256000</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.282</v>
+        <v>0.299</v>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         <v>-110</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-346296500</v>
+        <v>-336160000</v>
       </c>
       <c r="J41" s="16" t="n">
-        <v>-0.878</v>
+        <v>-0.946</v>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
@@ -1724,10 +1724,10 @@
         <v>27</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>48952350</v>
+        <v>42012000</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.124</v>
+        <v>0.118</v>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         <v>-76</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-40226800</v>
+        <v>-40432000</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>-0.102</v>
+        <v>-0.114</v>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         <v>25</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>327060000</v>
+        <v>263200000</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.829</v>
+        <v>0.741</v>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         <v>-32</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-46312960</v>
+        <v>-45209600</v>
       </c>
       <c r="J43" s="16" t="n">
-        <v>-0.117</v>
+        <v>-0.127</v>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         <v>23</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>102660500</v>
+        <v>93288000</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.26</v>
+        <v>0.263</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-24442600</v>
+        <v>-67984000</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-0.062</v>
+        <v>-0.191</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1844,10 +1844,10 @@
         <v>19</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>84656400</v>
+        <v>78736000</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.215</v>
+        <v>0.222</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-72000600</v>
+        <v>-23833600</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.183</v>
+        <v>-0.067</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1884,10 +1884,10 @@
         <v>12</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>63516000</v>
+        <v>53952000</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>-13</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-37331450</v>
+        <v>-36504000</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.095</v>
+        <v>-0.103</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         <v>11</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>26591400</v>
+        <v>19272000</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.067</v>
+        <v>0.054</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         <v>-12</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-19623600</v>
+        <v>-17347200</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.05</v>
+        <v>-0.049</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         <v>9</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>121367700</v>
+        <v>110952000</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>-9</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-76574700</v>
+        <v>-61920000</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.194</v>
+        <v>-0.174</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         <v>8</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>133668000</v>
+        <v>117120000</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.339</v>
+        <v>0.33</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>-9</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-118381500</v>
+        <v>-101304000</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.3</v>
+        <v>-0.285</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>53253900</v>
+        <v>47152000</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         <v>-5</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-105662500</v>
+        <v>-106200000</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-0.268</v>
+        <v>-0.299</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>21843500</v>
+        <v>19460000</v>
       </c>
       <c r="D51" s="12" t="n">
         <v>0.055</v>
@@ -2103,10 +2103,10 @@
         <v>-4</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-49706800</v>
+        <v>-39904000</v>
       </c>
       <c r="J51" s="16" t="n">
-        <v>-0.126</v>
+        <v>-0.112</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>67308000</v>
+        <v>97120000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.171</v>
+        <v>0.273</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>68→72</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2143,10 +2143,10 @@
         <v>-3</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-22041000</v>
+        <v>-20904000</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-0.056</v>
+        <v>-0.059</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>106966000</v>
+        <v>56896000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.271</v>
+        <v>0.16</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>68→72</t>
         </is>
       </c>
       <c r="G53" s="17" t="n"/>
@@ -2183,7 +2183,7 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 639억      주말 2026-07-03  vs  주초 2026-06-29      매수 3종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      주말 2026-07-03  vs  주초 2026-06-29      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -2279,10 +2279,10 @@
         <v>44</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>423442800</v>
+        <v>431072400</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>0.663</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
@@ -2298,10 +2298,10 @@
         <v>-622</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-780865020</v>
+        <v>-794934660</v>
       </c>
       <c r="J58" s="16" t="n">
-        <v>-1.223</v>
+        <v>-1.257</v>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         <v>32</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>632611200</v>
+        <v>644009600</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>0.991</v>
+        <v>1.018</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         <v>-17</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-663280500</v>
+        <v>-675231500</v>
       </c>
       <c r="J59" s="16" t="n">
-        <v>-1.039</v>
+        <v>-1.068</v>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         <v>13</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>629148000</v>
+        <v>640484000</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.985</v>
+        <v>1.013</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_weekly_20260703.xlsx
+++ b/reports/pdf_weekly_20260703.xlsx
@@ -1019,21 +1019,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2294943000</v>
+        <v>437344200</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.43</v>
+        <v>0.082</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1045,21 +1045,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>437344200</v>
+        <v>2294943000</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.082</v>
+        <v>0.43</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1816,21 +1816,21 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-67984000</v>
+        <v>-23833600</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-0.191</v>
+        <v>-0.067</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1856,21 +1856,21 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-23833600</v>
+        <v>-67984000</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.067</v>
+        <v>-0.191</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1976,21 +1976,21 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-61920000</v>
+        <v>-101304000</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.174</v>
+        <v>-0.285</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>140→131</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
@@ -2016,21 +2016,21 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-101304000</v>
+        <v>-61920000</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.285</v>
+        <v>-0.174</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>140→131</t>
         </is>
       </c>
     </row>
@@ -2117,21 +2117,21 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>97120000</v>
+        <v>56896000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.273</v>
+        <v>0.16</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>68→72</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2157,21 +2157,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>56896000</v>
+        <v>97120000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.16</v>
+        <v>0.273</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>68→72</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G53" s="17" t="n"/>

--- a/reports/pdf_weekly_20260703.xlsx
+++ b/reports/pdf_weekly_20260703.xlsx
@@ -1019,21 +1019,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>437344200</v>
+        <v>2294943000</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.082</v>
+        <v>0.43</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1045,21 +1045,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2294943000</v>
+        <v>437344200</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.43</v>
+        <v>0.082</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -2117,21 +2117,21 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>56896000</v>
+        <v>97120000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.16</v>
+        <v>0.273</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>68→72</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2157,21 +2157,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>97120000</v>
+        <v>56896000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.273</v>
+        <v>0.16</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>68→72</t>
         </is>
       </c>
       <c r="G53" s="17" t="n"/>

--- a/reports/pdf_weekly_20260703.xlsx
+++ b/reports/pdf_weekly_20260703.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -154,7 +153,7 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,7 +163,7 @@
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,11 +664,15 @@
       <c r="B6" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>563306120</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.105</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -684,11 +687,15 @@
       <c r="H6" s="15" t="n">
         <v>-57</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-5019591000</v>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>-0.9399999999999999</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -705,11 +712,15 @@
       <c r="B7" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>1488052500</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0.279</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -724,11 +735,15 @@
       <c r="H7" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-2739820300</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>-0.513</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -745,11 +760,15 @@
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>541714770</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0.101</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -764,11 +783,15 @@
       <c r="H8" s="15" t="n">
         <v>-46</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-4929406000</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>-0.923</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -785,11 +808,15 @@
       <c r="B9" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>1107206550</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0.207</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -804,11 +831,15 @@
       <c r="H9" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-514118160</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>-0.096</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -825,11 +856,15 @@
       <c r="B10" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>2093777400</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0.392</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -844,11 +879,15 @@
       <c r="H10" s="15" t="n">
         <v>-33</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-4681238100</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>-0.876</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -865,11 +904,15 @@
       <c r="B11" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>2094414000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0.392</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -884,11 +927,15 @@
       <c r="H11" s="15" t="n">
         <v>-24</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-2212821600</v>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>-0.414</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -905,11 +952,15 @@
       <c r="B12" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1926563800</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0.361</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -924,11 +975,15 @@
       <c r="H12" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-1733674000</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>-0.325</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -945,11 +1000,15 @@
       <c r="B13" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>541534400</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>0.101</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -964,11 +1023,15 @@
       <c r="H13" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-3087510000</v>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>-0.578</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -985,11 +1048,15 @@
       <c r="B14" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>1492827000</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>0.28</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1004,11 +1071,15 @@
       <c r="H14" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-783018000</v>
-      </c>
-      <c r="J14" s="16" t="n">
-        <v>-0.147</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1025,11 +1096,15 @@
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>2294943000</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>0.43</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -1051,11 +1126,15 @@
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>437344200</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>0.082</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1077,11 +1156,15 @@
       <c r="B17" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>459943500</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>0.08599999999999999</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1103,11 +1186,15 @@
       <c r="B18" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>1491766000</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0.279</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1129,11 +1216,15 @@
       <c r="B19" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>722541000</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0.135</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
@@ -1149,7 +1240,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      주말 2026-07-03  vs  주초 2026-06-29      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      주말 2026-07-03  vs  주초 2026-06-29      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1244,11 +1335,15 @@
       <c r="B24" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>454352880</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>0.094</v>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1263,11 +1358,15 @@
       <c r="H24" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I24" s="15" t="n">
-        <v>-1809472000</v>
-      </c>
-      <c r="J24" s="16" t="n">
-        <v>-0.372</v>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1284,11 +1383,15 @@
       <c r="B25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>1509432000</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>0.311</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1304,7 +1407,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,365억      주말 2026-07-03  vs  주초 2026-06-29      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      주말 2026-07-03  vs  주초 2026-06-29      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1399,11 +1502,15 @@
       <c r="B30" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>2532163200</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>0.752</v>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
@@ -1418,11 +1525,15 @@
       <c r="H30" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-2690192700</v>
-      </c>
-      <c r="J30" s="16" t="n">
-        <v>-0.799</v>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -1433,7 +1544,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,838억      주말 2026-07-03  vs  주초 2026-06-29      매수 0종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      주말 2026-07-03  vs  주초 2026-06-29      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1533,11 +1644,15 @@
       <c r="H35" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I35" s="15" t="n">
-        <v>-351434000</v>
-      </c>
-      <c r="J35" s="16" t="n">
-        <v>-0.124</v>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
@@ -1548,7 +1663,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 13종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      주말 2026-07-03  vs  주초 2026-06-29      매수 14종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1643,11 +1758,15 @@
       <c r="B40" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>63808000</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>0.18</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -1662,11 +1781,15 @@
       <c r="H40" s="15" t="n">
         <v>-111</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-216672000</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <v>-0.61</v>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
@@ -1683,11 +1806,15 @@
       <c r="B41" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>106256000</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>0.299</v>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
@@ -1702,11 +1829,15 @@
       <c r="H41" s="15" t="n">
         <v>-110</v>
       </c>
-      <c r="I41" s="15" t="n">
-        <v>-336160000</v>
-      </c>
-      <c r="J41" s="16" t="n">
-        <v>-0.946</v>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
@@ -1723,11 +1854,15 @@
       <c r="B42" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>42012000</v>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>0.118</v>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
@@ -1742,11 +1877,15 @@
       <c r="H42" s="15" t="n">
         <v>-76</v>
       </c>
-      <c r="I42" s="15" t="n">
-        <v>-40432000</v>
-      </c>
-      <c r="J42" s="16" t="n">
-        <v>-0.114</v>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
@@ -1763,11 +1902,15 @@
       <c r="B43" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>263200000</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>0.741</v>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
@@ -1782,11 +1925,15 @@
       <c r="H43" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I43" s="15" t="n">
-        <v>-45209600</v>
-      </c>
-      <c r="J43" s="16" t="n">
-        <v>-0.127</v>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
@@ -1803,11 +1950,15 @@
       <c r="B44" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>93288000</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <v>0.263</v>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -1816,21 +1967,25 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I44" s="15" t="n">
-        <v>-23833600</v>
-      </c>
-      <c r="J44" s="16" t="n">
-        <v>-0.067</v>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1843,11 +1998,15 @@
       <c r="B45" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>78736000</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>0.222</v>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1856,21 +2015,25 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-28</v>
       </c>
-      <c r="I45" s="15" t="n">
-        <v>-67984000</v>
-      </c>
-      <c r="J45" s="16" t="n">
-        <v>-0.191</v>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1883,11 +2046,15 @@
       <c r="B46" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>53952000</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>0.152</v>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1902,11 +2069,15 @@
       <c r="H46" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I46" s="15" t="n">
-        <v>-36504000</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>-0.103</v>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1923,11 +2094,15 @@
       <c r="B47" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>19272000</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>0.054</v>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1942,11 +2117,15 @@
       <c r="H47" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I47" s="15" t="n">
-        <v>-17347200</v>
-      </c>
-      <c r="J47" s="16" t="n">
-        <v>-0.049</v>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1963,11 +2142,15 @@
       <c r="B48" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>110952000</v>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>0.312</v>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -1982,11 +2165,15 @@
       <c r="H48" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-101304000</v>
-      </c>
-      <c r="J48" s="16" t="n">
-        <v>-0.285</v>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
@@ -2003,11 +2190,15 @@
       <c r="B49" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>117120000</v>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>0.33</v>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -2022,11 +2213,15 @@
       <c r="H49" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-61920000</v>
-      </c>
-      <c r="J49" s="16" t="n">
-        <v>-0.174</v>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
@@ -2043,11 +2238,15 @@
       <c r="B50" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>47152000</v>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>0.133</v>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2062,11 +2261,15 @@
       <c r="H50" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I50" s="15" t="n">
-        <v>-106200000</v>
-      </c>
-      <c r="J50" s="16" t="n">
-        <v>-0.299</v>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
@@ -2083,11 +2286,15 @@
       <c r="B51" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>19460000</v>
-      </c>
-      <c r="D51" s="12" t="n">
-        <v>0.055</v>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2102,11 +2309,15 @@
       <c r="H51" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-39904000</v>
-      </c>
-      <c r="J51" s="16" t="n">
-        <v>-0.112</v>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -2123,11 +2334,15 @@
       <c r="B52" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>97120000</v>
-      </c>
-      <c r="D52" s="12" t="n">
-        <v>0.273</v>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2142,11 +2357,15 @@
       <c r="H52" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-20904000</v>
-      </c>
-      <c r="J52" s="16" t="n">
-        <v>-0.059</v>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -2163,11 +2382,15 @@
       <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>56896000</v>
-      </c>
-      <c r="D53" s="12" t="n">
-        <v>0.16</v>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -2183,7 +2406,7 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      주말 2026-07-03  vs  주초 2026-06-29      매수 3종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      주말 2026-07-03  vs  주초 2026-06-29      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
@@ -2278,11 +2501,15 @@
       <c r="B58" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>431072400</v>
-      </c>
-      <c r="D58" s="12" t="n">
-        <v>0.6820000000000001</v>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
@@ -2297,11 +2524,15 @@
       <c r="H58" s="15" t="n">
         <v>-622</v>
       </c>
-      <c r="I58" s="15" t="n">
-        <v>-794934660</v>
-      </c>
-      <c r="J58" s="16" t="n">
-        <v>-1.257</v>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
@@ -2318,11 +2549,15 @@
       <c r="B59" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>644009600</v>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>1.018</v>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -2337,11 +2572,15 @@
       <c r="H59" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I59" s="15" t="n">
-        <v>-675231500</v>
-      </c>
-      <c r="J59" s="16" t="n">
-        <v>-1.068</v>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
@@ -2358,11 +2597,15 @@
       <c r="B60" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>640484000</v>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>1.013</v>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
